--- a/enterprise/documentation/TDengine resource estimate.xlsx
+++ b/enterprise/documentation/TDengine resource estimate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guanshengliang/work/TDinternal/enterprise/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E46AD45E-31D3-0043-BB40-D008AC8F4937}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21CBE4C9-8F47-824E-9751-494D399D92EE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="460" windowWidth="27780" windowHeight="17540" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2018的版本" sheetId="2" r:id="rId1"/>
@@ -1089,7 +1089,7 @@
     <author>建辉 陶</author>
   </authors>
   <commentList>
-    <comment ref="C21" authorId="0" shapeId="0" xr:uid="{4910350A-A79A-0042-B18A-55AB8F34FA6E}">
+    <comment ref="C23" authorId="0" shapeId="0" xr:uid="{4910350A-A79A-0042-B18A-55AB8F34FA6E}">
       <text>
         <r>
           <rPr>
@@ -1152,7 +1152,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C29" authorId="0" shapeId="0" xr:uid="{2F513179-20DC-9A46-BCD4-6A7ACA92726A}">
+    <comment ref="C35" authorId="0" shapeId="0" xr:uid="{2F513179-20DC-9A46-BCD4-6A7ACA92726A}">
       <text>
         <r>
           <rPr>
@@ -1220,7 +1220,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="55">
   <si>
     <t>Number of Columns</t>
   </si>
@@ -1355,6 +1355,36 @@
   </si>
   <si>
     <t>假设每个核每秒处理5000条写入请求</t>
+  </si>
+  <si>
+    <t>Number of Tables</t>
+  </si>
+  <si>
+    <t>Cache Block Size(MB)</t>
+  </si>
+  <si>
+    <t>Length of Tags for a Table (Bytes)</t>
+  </si>
+  <si>
+    <t>Length of Table Name (Bytes)</t>
+  </si>
+  <si>
+    <t>Row Size (Bytes)</t>
+  </si>
+  <si>
+    <t>Sampling Period (seconds)</t>
+  </si>
+  <si>
+    <t>Raw Data Per Day (GB)</t>
+  </si>
+  <si>
+    <t>Disk Increase Per Day (GB)</t>
+  </si>
+  <si>
+    <t>·</t>
+  </si>
+  <si>
+    <t>Total Memory Size (MB)</t>
   </si>
 </sst>
 </file>
@@ -2623,11 +2653,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{690791BA-8BC8-5747-92D2-597F1602CD16}">
-  <dimension ref="B2:D38"/>
+  <dimension ref="A2:D38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.1640625" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="2" max="2" width="35.83203125" customWidth="1"/>
     <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2647,7 +2677,7 @@
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>49</v>
       </c>
       <c r="C4" s="1">
         <v>32</v>
@@ -2655,7 +2685,7 @@
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="C5" s="1">
         <v>48</v>
@@ -2663,7 +2693,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C6" s="1">
         <v>64</v>
@@ -2679,7 +2709,7 @@
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="C8" s="1">
         <v>16</v>
@@ -2687,7 +2717,7 @@
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="C9" s="1">
         <v>100000</v>
@@ -2695,7 +2725,7 @@
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="C10" s="1">
         <v>10</v>
@@ -2745,7 +2775,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
@@ -2754,179 +2784,182 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="C18" s="2">
         <f xml:space="preserve"> C17*24*3600/1000</f>
         <v>27.648</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="C19" s="2">
         <f>C18*C12</f>
         <v>13.824</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="2">
+        <f xml:space="preserve"> C9 *24 * 3600 / C10</f>
+        <v>864000000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B21" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="2">
+        <f xml:space="preserve"> C20 * C3 / 86400</f>
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C22" s="2">
         <f>(C4*C11+60+28)*C15/C11*8/1000000</f>
         <v>2.6303999999999998</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B21" s="2" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C23" s="2">
         <f>(60+28)*C15*3600*24*30/C11/1000000/1000</f>
         <v>22.8096</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-    </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B23" s="6" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B25" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="6"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C26" s="2">
+        <f>CEILING(C16/5000,1)</f>
+        <v>1</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="5">
+        <f>CEILING(C26,2)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C23" s="6"/>
-    </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B24" s="1" t="s">
+      <c r="C29" s="6"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B30" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C30" s="1">
         <f>150+C5</f>
         <v>198</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B25" s="1" t="s">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B31" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C31" s="1">
         <f>350+C5+C6</f>
         <v>462</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B26" s="1" t="s">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B32" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="1">
-        <f>C24*C9/1000000</f>
+      <c r="C32" s="1">
+        <f>C30*C9/1000000</f>
         <v>19.8</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B27" s="1" t="s">
+    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B33" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="1">
-        <f>C8*C7*C34</f>
+      <c r="C33" s="1">
+        <f>C8*C7*C27</f>
         <v>192</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B28" s="1" t="s">
+    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B34" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="1">
-        <f>C25*C9/1000000</f>
+      <c r="C34" s="1">
+        <f>C31*C9/1000000</f>
         <v>46.2</v>
       </c>
     </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B29" s="1" t="s">
+    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B35" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C35" s="1">
         <f>512*C9/1000000</f>
         <v>51.2</v>
       </c>
     </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B30" s="2" t="s">
+    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B36" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C30" s="2">
-        <f>C7*C8*1000000/(C9/C34)/C4</f>
+      <c r="C36" s="2">
+        <f>C7*C8*1000000/(C9/C27)/C4</f>
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B31" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C31" s="2">
-        <f>C26+C27+C28+C29</f>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B37" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="2">
+        <f>C32+C33+C34+C35</f>
         <v>309.2</v>
       </c>
     </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B33" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C33" s="6"/>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B34" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" s="5">
-        <f>CEILING(C35,2)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B35" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C35" s="2">
-        <f>CEILING(C16/1000,1)</f>
-        <v>1</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B37" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C37" s="4">
-        <f xml:space="preserve"> C9 *24 * 3600 / C10</f>
-        <v>864000000</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B38" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C38" s="4">
-        <f xml:space="preserve"> C37 * C3 / 86400</f>
-        <v>30000</v>
-      </c>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B25:C25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
